--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.14990485039968</v>
+        <v>2.461859538189947</v>
       </c>
       <c r="D2" t="n">
-        <v>10.32972699888248</v>
+        <v>1.678580637318403</v>
       </c>
       <c r="E2" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F2" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.91753119677904</v>
+        <v>3.724098819476594</v>
       </c>
       <c r="D3" t="n">
-        <v>16.41502289728795</v>
+        <v>2.667441220809292</v>
       </c>
       <c r="E3" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F3" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>62.83625027296547</v>
+        <v>10.21089066935689</v>
       </c>
       <c r="D4" t="n">
-        <v>6.891774390742889</v>
+        <v>1.11991333849572</v>
       </c>
       <c r="E4" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F4" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>78.45554166615993</v>
+        <v>12.74902552075099</v>
       </c>
       <c r="D5" t="n">
-        <v>17.76333738163682</v>
+        <v>2.886542324515983</v>
       </c>
       <c r="E5" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F5" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.9344612738761</v>
+        <v>7.301849957004867</v>
       </c>
       <c r="D6" t="n">
-        <v>21.33512926982253</v>
+        <v>3.466958506346161</v>
       </c>
       <c r="E6" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F6" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.78624934521783</v>
+        <v>5.977765518597898</v>
       </c>
       <c r="D7" t="n">
-        <v>44.19937260737605</v>
+        <v>7.182398048698608</v>
       </c>
       <c r="E7" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F7" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>52.15573937716345</v>
+        <v>8.475307648789061</v>
       </c>
       <c r="D8" t="n">
-        <v>26.11826178022783</v>
+        <v>4.244217539287022</v>
       </c>
       <c r="E8" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F8" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.46170369529026</v>
+        <v>3.812526850484667</v>
       </c>
       <c r="D9" t="n">
-        <v>34.9746940028332</v>
+        <v>5.683387775460394</v>
       </c>
       <c r="E9" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F9" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.76025494058171</v>
+        <v>2.886041427844527</v>
       </c>
       <c r="D10" t="n">
-        <v>32.50298981701375</v>
+        <v>5.281735845264734</v>
       </c>
       <c r="E10" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F10" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>31.02136916034134</v>
+        <v>5.040972488555468</v>
       </c>
       <c r="D11" t="n">
-        <v>41.49551217970613</v>
+        <v>6.743020729202247</v>
       </c>
       <c r="E11" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F11" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>17.50750100131468</v>
+        <v>2.844968912713636</v>
       </c>
       <c r="D12" t="n">
-        <v>32.00099332539364</v>
+        <v>5.200161415376467</v>
       </c>
       <c r="E12" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F12" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>14.29536493642933</v>
+        <v>2.322996802169766</v>
       </c>
       <c r="D13" t="n">
-        <v>24.59503685190079</v>
+        <v>3.996693488433879</v>
       </c>
       <c r="E13" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F13" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>4.340339157199853</v>
+        <v>0.7053051130449762</v>
       </c>
       <c r="D14" t="n">
-        <v>15.66825237257621</v>
+        <v>2.546091010543635</v>
       </c>
       <c r="E14" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F14" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>19.06290097918122</v>
+        <v>3.097721409116948</v>
       </c>
       <c r="D15" t="n">
-        <v>22.28985256177797</v>
+        <v>3.62210104128892</v>
       </c>
       <c r="E15" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F15" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>31.06745120584338</v>
+        <v>5.048460820949549</v>
       </c>
       <c r="D16" t="n">
-        <v>34.91985526859744</v>
+        <v>5.674476481147084</v>
       </c>
       <c r="E16" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F16" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>34.836366340008</v>
+        <v>5.6609095302513</v>
       </c>
       <c r="D17" t="n">
-        <v>35.2540901839827</v>
+        <v>5.728789654897189</v>
       </c>
       <c r="E17" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F17" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>28.8162745165729</v>
+        <v>4.682644608943097</v>
       </c>
       <c r="D18" t="n">
-        <v>25.97960028696784</v>
+        <v>4.221685046632274</v>
       </c>
       <c r="E18" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F18" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>5.428601433134147</v>
+        <v>0.8821477328842989</v>
       </c>
       <c r="D19" t="n">
-        <v>9.953633870182582</v>
+        <v>1.61746550390467</v>
       </c>
       <c r="E19" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F19" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>19.81972287496588</v>
+        <v>3.220704967181955</v>
       </c>
       <c r="D20" t="n">
-        <v>16.30945443377611</v>
+        <v>2.650286345488618</v>
       </c>
       <c r="E20" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F20" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>23.25493502626356</v>
+        <v>3.778926941767828</v>
       </c>
       <c r="D21" t="n">
-        <v>34.21146961089607</v>
+        <v>5.559363811770611</v>
       </c>
       <c r="E21" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F21" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>11.44821151669046</v>
+        <v>1.8603343714622</v>
       </c>
       <c r="D22" t="n">
-        <v>12.45328499246173</v>
+        <v>2.02365881127503</v>
       </c>
       <c r="E22" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F22" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>21.29679887740626</v>
+        <v>3.460729817578517</v>
       </c>
       <c r="D23" t="n">
-        <v>21.69125240521577</v>
+        <v>3.524828515847563</v>
       </c>
       <c r="E23" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F23" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>68.17270343232559</v>
+        <v>11.07806430775291</v>
       </c>
       <c r="D24" t="n">
-        <v>59.77963457718344</v>
+        <v>9.71419061879231</v>
       </c>
       <c r="E24" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F24" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>54.53273571273716</v>
+        <v>8.861569553319789</v>
       </c>
       <c r="D25" t="n">
-        <v>54.73463191139019</v>
+        <v>8.894377685600906</v>
       </c>
       <c r="E25" t="n">
-        <v>19.44359606249258</v>
+        <v>3.159584360155045</v>
       </c>
       <c r="F25" t="n">
-        <v>13.48659407382215</v>
+        <v>2.1915715369961</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
